--- a/public_administration_forms/006_government_scheme_awareness_survey--public_administration_forms.xlsx
+++ b/public_administration_forms/006_government_scheme_awareness_survey--public_administration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -834,8 +834,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -863,12 +863,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_aware'}</t>
+          <t>very_aware</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very aware'}</t>
+          <t>Very aware</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_aware'}</t>
+          <t>somewhat_aware</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat aware'}</t>
+          <t>Somewhat aware</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_aware'}</t>
+          <t>not_aware</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not aware'}</t>
+          <t>Not aware</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -931,12 +931,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'tv'}</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'TV'}</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'radio'}</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Radio'}</t>
+          <t>Radio</t>
         </is>
       </c>
     </row>
@@ -965,12 +965,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -982,12 +982,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'social_media'}</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Social media'}</t>
+          <t>Social media</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1050,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'tv'}</t>
+          <t>tv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'TV'}</t>
+          <t>TV</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1067,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'radio'}</t>
+          <t>radio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Radio'}</t>
+          <t>Radio</t>
         </is>
       </c>
     </row>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'friend'}</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Friend'}</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'family'}</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Family'}</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'easy'}</t>
+          <t>easy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Easy'}</t>
+          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_easy'}</t>
+          <t>somewhat_easy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat easy'}</t>
+          <t>Somewhat easy</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_easy'}</t>
+          <t>not_easy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not easy'}</t>
+          <t>Not easy</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_possible'}</t>
+          <t>not_possible</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not possible'}</t>
+          <t>Not possible</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'language_barrier'}</t>
+          <t>language_barrier</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Language barrier'}</t>
+          <t>Language barrier</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_awareness'}</t>
+          <t>lack_of_awareness</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of awareness'}</t>
+          <t>Lack of awareness</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_interest'}</t>
+          <t>lack_of_interest</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of interest'}</t>
+          <t>Lack of interest</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'lack_of_skills'}</t>
+          <t>lack_of_skills</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Lack of skills'}</t>
+          <t>Lack of skills</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
